--- a/Thesis Forecasting/metadata/overall_comparison/model_average_validation_testing_comparison.xlsx
+++ b/Thesis Forecasting/metadata/overall_comparison/model_average_validation_testing_comparison.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>158</v>
+        <v>234</v>
       </c>
       <c r="D2" t="n">
-        <v>3.475919113707131</v>
+        <v>3.476164999616764</v>
       </c>
       <c r="E2" t="n">
-        <v>1.840847984937388</v>
+        <v>1.841105299238234</v>
       </c>
       <c r="F2" t="n">
-        <v>3.440295102101322</v>
+        <v>3.440686379843341</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8988599585985897</v>
+        <v>0.8988369512132961</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -514,19 +514,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="D3" t="n">
-        <v>3.486362417005194</v>
+        <v>3.377216762221778</v>
       </c>
       <c r="E3" t="n">
-        <v>1.875336494578505</v>
+        <v>1.83697522051419</v>
       </c>
       <c r="F3" t="n">
-        <v>3.427619689013735</v>
+        <v>3.3902379831123</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8996038657827569</v>
+        <v>0.9017817700204243</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="D4" t="n">
-        <v>3.572705810229515</v>
+        <v>3.393549742790847</v>
       </c>
       <c r="E4" t="n">
-        <v>1.928287727407958</v>
+        <v>1.838306842486888</v>
       </c>
       <c r="F4" t="n">
-        <v>3.507520889972095</v>
+        <v>3.313260015069622</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8948686441752667</v>
+        <v>0.9061913747309848</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -578,19 +578,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>158</v>
+        <v>234</v>
       </c>
       <c r="D5" t="n">
-        <v>3.471231035467674</v>
+        <v>3.469709109951022</v>
       </c>
       <c r="E5" t="n">
-        <v>1.726776719652155</v>
+        <v>1.726094758945026</v>
       </c>
       <c r="F5" t="n">
-        <v>2.755809174796953</v>
+        <v>2.756650895208767</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9290627965976143</v>
+        <v>0.9290194565788212</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="D6" t="n">
-        <v>3.52859002181966</v>
+        <v>3.386005159095108</v>
       </c>
       <c r="E6" t="n">
-        <v>1.739151711725675</v>
+        <v>1.678480657713253</v>
       </c>
       <c r="F6" t="n">
-        <v>2.807124889541247</v>
+        <v>2.675410175200322</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9263963672885636</v>
+        <v>0.9331415154238221</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="D7" t="n">
-        <v>3.451840791241192</v>
+        <v>3.419576431509979</v>
       </c>
       <c r="E7" t="n">
-        <v>1.71664344441512</v>
+        <v>1.699455653952136</v>
       </c>
       <c r="F7" t="n">
-        <v>2.769457742259154</v>
+        <v>2.686937387670291</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9283584018428611</v>
+        <v>0.932564144329582</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="D8" t="n">
         <v>1.372393407127368</v>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>2.161182022518592</v>
+        <v>2.360647957762337</v>
       </c>
       <c r="E9" t="n">
-        <v>1.933811975752544</v>
+        <v>2.057751859712116</v>
       </c>
       <c r="F9" t="n">
-        <v>5.005367101266894</v>
+        <v>4.894579628714905</v>
       </c>
       <c r="G9" t="n">
-        <v>0.904776404097143</v>
+        <v>0.9089450616528172</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>2.553581038972992</v>
+        <v>2.596536026075724</v>
       </c>
       <c r="E10" t="n">
-        <v>2.173190188862365</v>
+        <v>2.346439887403684</v>
       </c>
       <c r="F10" t="n">
-        <v>5.219189186025636</v>
+        <v>5.164883681643188</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8964670027188831</v>
+        <v>0.8986103092469176</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="D11" t="n">
-        <v>1.080237388266095</v>
+        <v>1.080237414062809</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9836404595910582</v>
+        <v>0.9836404855962289</v>
       </c>
       <c r="F11" t="n">
-        <v>4.296788174711516</v>
+        <v>4.296788179362019</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8217338979659277</v>
+        <v>0.8217338975800454</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -802,19 +802,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D12" t="n">
-        <v>2.197333539992933</v>
+        <v>1.346888884370499</v>
       </c>
       <c r="E12" t="n">
-        <v>2.144955981389472</v>
+        <v>1.234468312569503</v>
       </c>
       <c r="F12" t="n">
-        <v>4.534518648274945</v>
+        <v>4.150251280106098</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8014621728253392</v>
+        <v>0.8336856723563233</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -834,19 +834,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D13" t="n">
-        <v>1.744494832966965</v>
+        <v>1.403638972068982</v>
       </c>
       <c r="E13" t="n">
-        <v>1.620137456758978</v>
+        <v>1.291389617967789</v>
       </c>
       <c r="F13" t="n">
-        <v>4.236730177584649</v>
+        <v>4.10041242645813</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8266824694896371</v>
+        <v>0.8376561047942912</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6106872916793786</v>
+        <v>0.6106872916782813</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6974508930056273</v>
+        <v>0.6974508930041152</v>
       </c>
       <c r="F14" t="n">
-        <v>3.077447039614186</v>
+        <v>3.07744703961429</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9453153141242143</v>
+        <v>0.9453153141242105</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -898,19 +898,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D15" t="n">
-        <v>1.164311265066937</v>
+        <v>0.8368764813740764</v>
       </c>
       <c r="E15" t="n">
-        <v>1.365183498334776</v>
+        <v>0.9950894832429902</v>
       </c>
       <c r="F15" t="n">
-        <v>3.454070031467231</v>
+        <v>2.926018781429621</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9311114849194968</v>
+        <v>0.9505645189020273</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -930,19 +930,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D16" t="n">
-        <v>1.05126148122372</v>
+        <v>1.152639285327153</v>
       </c>
       <c r="E16" t="n">
-        <v>1.26574175268856</v>
+        <v>1.433715598698781</v>
       </c>
       <c r="F16" t="n">
-        <v>3.272789934700768</v>
+        <v>3.117158386064567</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9381526910348479</v>
+        <v>0.943894907113505</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -962,19 +962,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8267609583386537</v>
+        <v>0.8267609624278227</v>
       </c>
       <c r="E17" t="n">
-        <v>0.716515938221218</v>
+        <v>0.7165159423868309</v>
       </c>
       <c r="F17" t="n">
-        <v>3.362162388246943</v>
+        <v>3.362162393322077</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9528117569485496</v>
+        <v>0.9528117568060896</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D18" t="n">
-        <v>1.774556659412656</v>
+        <v>1.226140381658184</v>
       </c>
       <c r="E18" t="n">
-        <v>1.456443027139064</v>
+        <v>1.100333454368979</v>
       </c>
       <c r="F18" t="n">
-        <v>3.980111616750163</v>
+        <v>3.26922366793582</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9338717637429117</v>
+        <v>0.9553845060592133</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D19" t="n">
-        <v>1.71745827658513</v>
+        <v>1.298614718107114</v>
       </c>
       <c r="E19" t="n">
-        <v>1.382999808041294</v>
+        <v>1.190482377494922</v>
       </c>
       <c r="F19" t="n">
-        <v>3.902914547977252</v>
+        <v>3.196609837158374</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9364120941983439</v>
+        <v>0.9573444348960065</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="D20" t="n">
         <v>4.039603029011061</v>
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D21" t="n">
-        <v>4.200484513643534</v>
+        <v>4.08064247874045</v>
       </c>
       <c r="E21" t="n">
-        <v>1.598433789599624</v>
+        <v>1.572321523955471</v>
       </c>
       <c r="F21" t="n">
-        <v>2.268945184641984</v>
+        <v>2.192159151310138</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8932760677734746</v>
+        <v>0.9003773769971353</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D22" t="n">
-        <v>4.227887501466392</v>
+        <v>4.602579242371828</v>
       </c>
       <c r="E22" t="n">
-        <v>1.614116089819198</v>
+        <v>1.810201869515812</v>
       </c>
       <c r="F22" t="n">
-        <v>2.233242150647068</v>
+        <v>2.416508167953064</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8966083555186281</v>
+        <v>0.8789428778386892</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="D23" t="n">
-        <v>4.090822638647039</v>
+        <v>4.090822638847586</v>
       </c>
       <c r="E23" t="n">
-        <v>1.469152401165102</v>
+        <v>1.469152401234568</v>
       </c>
       <c r="F23" t="n">
-        <v>2.231269481513257</v>
+        <v>2.231269481635627</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9043404627666414</v>
+        <v>0.9043404627561488</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D24" t="n">
-        <v>4.181556633756847</v>
+        <v>3.964092083803105</v>
       </c>
       <c r="E24" t="n">
-        <v>1.491315664584439</v>
+        <v>1.415609857474836</v>
       </c>
       <c r="F24" t="n">
-        <v>2.224479677726016</v>
+        <v>2.12653277869198</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9049217652560917</v>
+        <v>0.9131102820191399</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1218,19 +1218,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D25" t="n">
-        <v>4.180765718437955</v>
+        <v>3.981715159288837</v>
       </c>
       <c r="E25" t="n">
-        <v>1.479533045060711</v>
+        <v>1.418838059082079</v>
       </c>
       <c r="F25" t="n">
-        <v>2.188924444285949</v>
+        <v>2.102737943311137</v>
       </c>
       <c r="G25" t="n">
-        <v>0.907936863415191</v>
+        <v>0.9150439077442523</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>171</v>
+        <v>307</v>
       </c>
       <c r="D26" t="n">
         <v>1.404527208907398</v>
@@ -1282,19 +1282,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="D27" t="n">
-        <v>19.87941386644245</v>
+        <v>4.14007245328403</v>
       </c>
       <c r="E27" t="n">
-        <v>8.033408364487512</v>
+        <v>2.912237979858503</v>
       </c>
       <c r="F27" t="n">
-        <v>12.19846815910361</v>
+        <v>6.080681074686011</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9560946692216128</v>
+        <v>0.9890903426365119</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="D28" t="n">
-        <v>37.5409989513803</v>
+        <v>9.658712339399798</v>
       </c>
       <c r="E28" t="n">
-        <v>14.05841895127159</v>
+        <v>5.270241597014518</v>
       </c>
       <c r="F28" t="n">
-        <v>22.57904593416176</v>
+        <v>7.47642427112801</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8495757572901768</v>
+        <v>0.9835071945146232</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1346,19 +1346,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>171</v>
+        <v>307</v>
       </c>
       <c r="D29" t="n">
-        <v>2.412584472589698</v>
+        <v>2.41258447264652</v>
       </c>
       <c r="E29" t="n">
-        <v>3.667330521179721</v>
+        <v>3.667330521262003</v>
       </c>
       <c r="F29" t="n">
-        <v>7.981140072128379</v>
+        <v>7.981140072098497</v>
       </c>
       <c r="G29" t="n">
-        <v>0.83490126947832</v>
+        <v>0.8349012694795562</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1378,19 +1378,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="D30" t="n">
-        <v>2.967630624280723</v>
+        <v>2.464661547382927</v>
       </c>
       <c r="E30" t="n">
-        <v>4.534963565508413</v>
+        <v>3.71714037173041</v>
       </c>
       <c r="F30" t="n">
-        <v>8.150774218763839</v>
+        <v>7.331512491350271</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8278085456100657</v>
+        <v>0.8606839906494381</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1410,19 +1410,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="D31" t="n">
-        <v>2.664091660721063</v>
+        <v>2.615445612548182</v>
       </c>
       <c r="E31" t="n">
-        <v>4.047043590636704</v>
+        <v>3.923876505981132</v>
       </c>
       <c r="F31" t="n">
-        <v>7.62303727279962</v>
+        <v>7.440075999279395</v>
       </c>
       <c r="G31" t="n">
-        <v>0.849384400566642</v>
+        <v>0.8565275179102061</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1442,19 +1442,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="D32" t="n">
-        <v>4.209301696521237</v>
+        <v>4.209301696541133</v>
       </c>
       <c r="E32" t="n">
-        <v>1.490988678325157</v>
+        <v>1.490988678326474</v>
       </c>
       <c r="F32" t="n">
-        <v>2.254351155379669</v>
+        <v>2.254351155380284</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9046698091595458</v>
+        <v>0.9046698091594937</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1474,19 +1474,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D33" t="n">
-        <v>4.294212888621112</v>
+        <v>4.149024259946129</v>
       </c>
       <c r="E33" t="n">
-        <v>1.526733463455669</v>
+        <v>1.47161523248911</v>
       </c>
       <c r="F33" t="n">
-        <v>2.174929166543046</v>
+        <v>2.076160785216743</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9112685527839555</v>
+        <v>0.9191445501317088</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D34" t="n">
-        <v>4.31108012753736</v>
+        <v>3.852817953240654</v>
       </c>
       <c r="E34" t="n">
-        <v>1.542352377302068</v>
+        <v>1.354018360421051</v>
       </c>
       <c r="F34" t="n">
-        <v>2.173520856365352</v>
+        <v>1.948228090654059</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9113834263574155</v>
+        <v>0.9288021413168979</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="D35" t="n">
-        <v>3.806185782809625</v>
+        <v>3.806185784546269</v>
       </c>
       <c r="E35" t="n">
-        <v>1.233536460413938</v>
+        <v>1.23353646090493</v>
       </c>
       <c r="F35" t="n">
-        <v>2.109282641716446</v>
+        <v>2.109282641922523</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8242055587670627</v>
+        <v>0.8242055587327124</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1570,19 +1570,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D36" t="n">
-        <v>4.182444181484814</v>
+        <v>3.730500739807862</v>
       </c>
       <c r="E36" t="n">
-        <v>1.343362405314368</v>
+        <v>1.197703904692743</v>
       </c>
       <c r="F36" t="n">
-        <v>2.089475624941428</v>
+        <v>1.955127140382782</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8274916190187004</v>
+        <v>0.8489622213067463</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1602,19 +1602,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D37" t="n">
-        <v>4.083274772187985</v>
+        <v>3.666833690136424</v>
       </c>
       <c r="E37" t="n">
-        <v>1.314191121949027</v>
+        <v>1.171925912428912</v>
       </c>
       <c r="F37" t="n">
-        <v>2.057274702140808</v>
+        <v>1.89522074726815</v>
       </c>
       <c r="G37" t="n">
-        <v>0.832767704050032</v>
+        <v>0.8580762150003438</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>

--- a/Thesis Forecasting/metadata/overall_comparison/model_average_validation_testing_comparison.xlsx
+++ b/Thesis Forecasting/metadata/overall_comparison/model_average_validation_testing_comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$H$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$M$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,17 +415,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,6 +471,31 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>evaluation_type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>mape_rows_included</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>mape_rows_excluded</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>mape_rows_excluded_fraction</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>low_load_regime</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>split</t>
         </is>
       </c>
@@ -482,21 +512,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="D2" t="n">
-        <v>3.476164999616764</v>
+        <v>5.793521167859188</v>
       </c>
       <c r="E2" t="n">
-        <v>1.841105299238234</v>
+        <v>3.18322446163071</v>
       </c>
       <c r="F2" t="n">
-        <v>3.440686379843341</v>
+        <v>7.967810392425083</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8988369512132961</v>
+        <v>0.4855949283007271</v>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -514,21 +561,38 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="D3" t="n">
-        <v>3.377216762221778</v>
+        <v>6.215945628090261</v>
       </c>
       <c r="E3" t="n">
-        <v>1.83697522051419</v>
+        <v>3.430201051548947</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3902379831123</v>
+        <v>8.159118872191195</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9017817700204243</v>
+        <v>0.4605964736754846</v>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -546,21 +610,38 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="D4" t="n">
-        <v>3.393549742790847</v>
+        <v>14.89827152521508</v>
       </c>
       <c r="E4" t="n">
-        <v>1.838306842486888</v>
+        <v>8.374156805655712</v>
       </c>
       <c r="F4" t="n">
-        <v>3.313260015069622</v>
+        <v>12.32075573692778</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9061913747309848</v>
+        <v>-0.2299910619096863</v>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -578,21 +659,38 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="D5" t="n">
-        <v>3.469709109951022</v>
+        <v>6.0864857590444</v>
       </c>
       <c r="E5" t="n">
-        <v>1.726094758945026</v>
+        <v>2.767526559323921</v>
       </c>
       <c r="F5" t="n">
-        <v>2.756650895208767</v>
+        <v>5.275448123668693</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9290194565788212</v>
+        <v>0.7105267273879203</v>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -610,21 +708,38 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="D6" t="n">
-        <v>3.386005159095108</v>
+        <v>6.000803769673537</v>
       </c>
       <c r="E6" t="n">
-        <v>1.678480657713253</v>
+        <v>2.6627651011469</v>
       </c>
       <c r="F6" t="n">
-        <v>2.675410175200322</v>
+        <v>5.333464416346492</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9331415154238221</v>
+        <v>0.7041248021227725</v>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -642,21 +757,38 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="D7" t="n">
-        <v>3.419576431509979</v>
+        <v>12.67904447374227</v>
       </c>
       <c r="E7" t="n">
-        <v>1.699455653952136</v>
+        <v>6.199859678247157</v>
       </c>
       <c r="F7" t="n">
-        <v>2.686937387670291</v>
+        <v>9.053472191828156</v>
       </c>
       <c r="G7" t="n">
-        <v>0.932564144329582</v>
+        <v>0.1474495234600094</v>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -674,21 +806,38 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D8" t="n">
-        <v>1.372393407127368</v>
+        <v>5.503947012698498</v>
       </c>
       <c r="E8" t="n">
-        <v>1.163875279835391</v>
+        <v>4.618375436582778</v>
       </c>
       <c r="F8" t="n">
-        <v>4.810318338249981</v>
+        <v>11.22967598524945</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9120531387836908</v>
+        <v>0.516724948633329</v>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -706,21 +855,38 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>2.360647957762337</v>
+        <v>13.56293254451962</v>
       </c>
       <c r="E9" t="n">
-        <v>2.057751859712116</v>
+        <v>14.06390543319609</v>
       </c>
       <c r="F9" t="n">
-        <v>4.894579628714905</v>
+        <v>19.57208479661322</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9089450616528172</v>
+        <v>-0.4680271984640838</v>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -738,21 +904,38 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>2.596536026075724</v>
+        <v>11.11757252065611</v>
       </c>
       <c r="E10" t="n">
-        <v>2.346439887403684</v>
+        <v>11.08684116555558</v>
       </c>
       <c r="F10" t="n">
-        <v>5.164883681643188</v>
+        <v>15.96858331402931</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8986103092469176</v>
+        <v>0.02277920160870939</v>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -770,21 +953,38 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D11" t="n">
-        <v>1.080237414062809</v>
+        <v>4.295800144595013</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9836404855962289</v>
+        <v>3.932858840961659</v>
       </c>
       <c r="F11" t="n">
-        <v>4.296788179362019</v>
+        <v>8.889578621557694</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8217338975800454</v>
+        <v>0.2965521284193977</v>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -802,21 +1002,38 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D12" t="n">
-        <v>1.346888884370499</v>
+        <v>9.433533752805115</v>
       </c>
       <c r="E12" t="n">
-        <v>1.234468312569503</v>
+        <v>9.508270380055633</v>
       </c>
       <c r="F12" t="n">
-        <v>4.150251280106098</v>
+        <v>12.9244615490271</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8336856723563233</v>
+        <v>-0.4869435693024888</v>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -834,21 +1051,38 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D13" t="n">
-        <v>1.403638972068982</v>
+        <v>8.012625712616954</v>
       </c>
       <c r="E13" t="n">
-        <v>1.291389617967789</v>
+        <v>7.965410476549016</v>
       </c>
       <c r="F13" t="n">
-        <v>4.10041242645813</v>
+        <v>11.44105689872277</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8376561047942912</v>
+        <v>-0.1652037139806954</v>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -866,21 +1100,38 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6106872916782813</v>
+        <v>2.257292839824642</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6974508930041152</v>
+        <v>2.411839192371335</v>
       </c>
       <c r="F14" t="n">
-        <v>3.07744703961429</v>
+        <v>7.954289216601523</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9453153141242105</v>
+        <v>0.6351548356956079</v>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -898,21 +1149,38 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8368764813740764</v>
+        <v>7.240780251485892</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9950894832429902</v>
+        <v>9.178163714670596</v>
       </c>
       <c r="F15" t="n">
-        <v>2.926018781429621</v>
+        <v>11.19566518503113</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9505645189020273</v>
+        <v>0.2772208050725247</v>
       </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -930,21 +1198,38 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D16" t="n">
-        <v>1.152639285327153</v>
+        <v>6.021769925483243</v>
       </c>
       <c r="E16" t="n">
-        <v>1.433715598698781</v>
+        <v>7.438204439875792</v>
       </c>
       <c r="F16" t="n">
-        <v>3.117158386064567</v>
+        <v>10.783571771579</v>
       </c>
       <c r="G16" t="n">
-        <v>0.943894907113505</v>
+        <v>0.3294500951967373</v>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -962,21 +1247,38 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8267609624278227</v>
+        <v>3.541045909138147</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7165159423868309</v>
+        <v>2.984570972411286</v>
       </c>
       <c r="F17" t="n">
-        <v>3.362162393322077</v>
+        <v>9.636795959124711</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9528117568060896</v>
+        <v>0.6073764754997955</v>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -994,21 +1296,38 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D18" t="n">
-        <v>1.226140381658184</v>
+        <v>6.404062237925282</v>
       </c>
       <c r="E18" t="n">
-        <v>1.100333454368979</v>
+        <v>6.206076404744769</v>
       </c>
       <c r="F18" t="n">
-        <v>3.26922366793582</v>
+        <v>8.927914667286146</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9553845060592133</v>
+        <v>0.6630146265218528</v>
       </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -1026,21 +1345,38 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D19" t="n">
-        <v>1.298614718107114</v>
+        <v>5.759259863862858</v>
       </c>
       <c r="E19" t="n">
-        <v>1.190482377494922</v>
+        <v>5.377330824484067</v>
       </c>
       <c r="F19" t="n">
-        <v>3.196609837158374</v>
+        <v>11.9102742084685</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9573444348960065</v>
+        <v>0.400271744693631</v>
       </c>
       <c r="H19" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -1058,21 +1394,38 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D20" t="n">
-        <v>4.039603029011061</v>
+        <v>6.914546868482034</v>
       </c>
       <c r="E20" t="n">
-        <v>1.543745650205762</v>
+        <v>2.628291897104535</v>
       </c>
       <c r="F20" t="n">
-        <v>2.189078855121269</v>
+        <v>3.775856572479338</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9006571482808045</v>
+        <v>0.7252522406759934</v>
       </c>
       <c r="H20" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -1090,21 +1443,38 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D21" t="n">
-        <v>4.08064247874045</v>
+        <v>7.681789547555446</v>
       </c>
       <c r="E21" t="n">
-        <v>1.572321523955471</v>
+        <v>2.703064009264373</v>
       </c>
       <c r="F21" t="n">
-        <v>2.192159151310138</v>
+        <v>3.814856253627946</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9003773769971353</v>
+        <v>0.7195473569291837</v>
       </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -1122,21 +1492,38 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D22" t="n">
-        <v>4.602579242371828</v>
+        <v>7.531215584620392</v>
       </c>
       <c r="E22" t="n">
-        <v>1.810201869515812</v>
+        <v>2.668592610358417</v>
       </c>
       <c r="F22" t="n">
-        <v>2.416508167953064</v>
+        <v>3.876753823489376</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8789428778386892</v>
+        <v>0.7103726111456587</v>
       </c>
       <c r="H22" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -1154,21 +1541,38 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D23" t="n">
-        <v>4.090822638847586</v>
+        <v>8.310013182469508</v>
       </c>
       <c r="E23" t="n">
-        <v>1.469152401234568</v>
+        <v>2.768804497769296</v>
       </c>
       <c r="F23" t="n">
-        <v>2.231269481635627</v>
+        <v>4.660559898748315</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9043404627561488</v>
+        <v>0.5279108308705944</v>
       </c>
       <c r="H23" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -1186,21 +1590,38 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D24" t="n">
-        <v>3.964092083803105</v>
+        <v>10.59869591759488</v>
       </c>
       <c r="E24" t="n">
-        <v>1.415609857474836</v>
+        <v>3.363195309150354</v>
       </c>
       <c r="F24" t="n">
-        <v>2.12653277869198</v>
+        <v>5.037048038015321</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9131102820191399</v>
+        <v>0.4485577542149736</v>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -1218,21 +1639,38 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D25" t="n">
-        <v>3.981715159288837</v>
+        <v>9.792670650301922</v>
       </c>
       <c r="E25" t="n">
-        <v>1.418838059082079</v>
+        <v>3.047561809257031</v>
       </c>
       <c r="F25" t="n">
-        <v>2.102737943311137</v>
+        <v>4.714574207131379</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9150439077442523</v>
+        <v>0.516904713062379</v>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -1250,21 +1688,38 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="D26" t="n">
-        <v>1.404527208907398</v>
+        <v>6.942901795769707</v>
       </c>
       <c r="E26" t="n">
-        <v>1.395706172839505</v>
+        <v>5.472142688975849</v>
       </c>
       <c r="F26" t="n">
-        <v>5.678938424204445</v>
+        <v>16.54079834570621</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9904842947984128</v>
+        <v>0.9188709960649202</v>
       </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -1282,21 +1737,38 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="D27" t="n">
-        <v>4.14007245328403</v>
+        <v>14.76437356829242</v>
       </c>
       <c r="E27" t="n">
-        <v>2.912237979858503</v>
+        <v>16.38180457423511</v>
       </c>
       <c r="F27" t="n">
-        <v>6.080681074686011</v>
+        <v>28.78120354009989</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9890903426365119</v>
+        <v>0.754370167839102</v>
       </c>
       <c r="H27" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -1314,21 +1786,38 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="D28" t="n">
-        <v>9.658712339399798</v>
+        <v>11.32169312369476</v>
       </c>
       <c r="E28" t="n">
-        <v>5.270241597014518</v>
+        <v>12.22954181132504</v>
       </c>
       <c r="F28" t="n">
-        <v>7.47642427112801</v>
+        <v>22.41959472589807</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9835071945146232</v>
+        <v>0.8509545491074079</v>
       </c>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -1346,21 +1835,38 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="D29" t="n">
-        <v>2.41258447264652</v>
+        <v>7.29517979256501</v>
       </c>
       <c r="E29" t="n">
-        <v>3.667330521262003</v>
+        <v>11.15462139875414</v>
       </c>
       <c r="F29" t="n">
-        <v>7.981140072098497</v>
+        <v>18.97973631052641</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8349012694795562</v>
+        <v>0.07575634502367157</v>
       </c>
       <c r="H29" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -1378,21 +1884,38 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="D30" t="n">
-        <v>2.464661547382927</v>
+        <v>21.85123707655707</v>
       </c>
       <c r="E30" t="n">
-        <v>3.71714037173041</v>
+        <v>33.6250420990585</v>
       </c>
       <c r="F30" t="n">
-        <v>7.331512491350271</v>
+        <v>40.54989051433547</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8606839906494381</v>
+        <v>-3.218766617977598</v>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -1410,21 +1933,38 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="D31" t="n">
-        <v>2.615445612548182</v>
+        <v>12.84559291283292</v>
       </c>
       <c r="E31" t="n">
-        <v>3.923876505981132</v>
+        <v>19.75635822675999</v>
       </c>
       <c r="F31" t="n">
-        <v>7.440075999279395</v>
+        <v>26.61372465755518</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8565275179102061</v>
+        <v>-0.8172615919632893</v>
       </c>
       <c r="H31" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -1442,21 +1982,38 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D32" t="n">
-        <v>4.209301696541133</v>
+        <v>7.409128287893188</v>
       </c>
       <c r="E32" t="n">
-        <v>1.490988678326474</v>
+        <v>2.593457805828454</v>
       </c>
       <c r="F32" t="n">
-        <v>2.254351155380284</v>
+        <v>3.495672442815243</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9046698091594937</v>
+        <v>0.7747912657532339</v>
       </c>
       <c r="H32" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -1474,21 +2031,38 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D33" t="n">
-        <v>4.149024259946129</v>
+        <v>6.65501983293405</v>
       </c>
       <c r="E33" t="n">
-        <v>1.47161523248911</v>
+        <v>2.263569947475957</v>
       </c>
       <c r="F33" t="n">
-        <v>2.076160785216743</v>
+        <v>3.267329231872592</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9191445501317088</v>
+        <v>0.8032523451372638</v>
       </c>
       <c r="H33" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -1506,21 +2080,38 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>3.852817953240654</v>
+        <v>8.038243618227868</v>
       </c>
       <c r="E34" t="n">
-        <v>1.354018360421051</v>
+        <v>2.630714025191922</v>
       </c>
       <c r="F34" t="n">
-        <v>1.948228090654059</v>
+        <v>3.667494929248991</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9288021413168979</v>
+        <v>0.7521078284119701</v>
       </c>
       <c r="H34" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
@@ -1538,21 +2129,38 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D35" t="n">
-        <v>3.806185784546269</v>
+        <v>7.623169754489648</v>
       </c>
       <c r="E35" t="n">
-        <v>1.23353646090493</v>
+        <v>2.459417664679759</v>
       </c>
       <c r="F35" t="n">
-        <v>2.109282641922523</v>
+        <v>3.585699267928486</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8242055587327124</v>
+        <v>0.4739810586016601</v>
       </c>
       <c r="H35" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -1570,21 +2178,38 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D36" t="n">
-        <v>3.730500739807862</v>
+        <v>8.409529152993814</v>
       </c>
       <c r="E36" t="n">
-        <v>1.197703904692743</v>
+        <v>2.686670245758572</v>
       </c>
       <c r="F36" t="n">
-        <v>1.955127140382782</v>
+        <v>3.81798511102792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8489622213067463</v>
+        <v>0.4036213071998926</v>
       </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
@@ -1602,28 +2227,45 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D37" t="n">
-        <v>3.666833690136424</v>
+        <v>13.84199780817706</v>
       </c>
       <c r="E37" t="n">
-        <v>1.171925912428912</v>
+        <v>4.323162675903657</v>
       </c>
       <c r="F37" t="n">
-        <v>1.89522074726815</v>
+        <v>5.73075663185077</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8580762150003438</v>
+        <v>-0.3436234941615954</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
           <t>validation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H37"/>
+  <autoFilter ref="A1:M37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Thesis Forecasting/metadata/overall_comparison/model_average_validation_testing_comparison.xlsx
+++ b/Thesis Forecasting/metadata/overall_comparison/model_average_validation_testing_comparison.xlsx
@@ -515,16 +515,16 @@
         <v>203</v>
       </c>
       <c r="D2" t="n">
-        <v>5.793521167859188</v>
+        <v>5.948577545752768</v>
       </c>
       <c r="E2" t="n">
-        <v>3.18322446163071</v>
+        <v>3.275663779475344</v>
       </c>
       <c r="F2" t="n">
-        <v>7.967810392425083</v>
+        <v>8.048516433447602</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4855949283007271</v>
+        <v>0.4751213224448884</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -564,16 +564,16 @@
         <v>203</v>
       </c>
       <c r="D3" t="n">
-        <v>6.215945628090261</v>
+        <v>5.815498951255169</v>
       </c>
       <c r="E3" t="n">
-        <v>3.430201051548947</v>
+        <v>3.178357148433609</v>
       </c>
       <c r="F3" t="n">
-        <v>8.159118872191195</v>
+        <v>8.03495817340387</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4605964736754846</v>
+        <v>0.4768882188913155</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -613,16 +613,16 @@
         <v>203</v>
       </c>
       <c r="D4" t="n">
-        <v>14.89827152521508</v>
+        <v>6.554836238848782</v>
       </c>
       <c r="E4" t="n">
-        <v>8.374156805655712</v>
+        <v>3.511287228809579</v>
       </c>
       <c r="F4" t="n">
-        <v>12.32075573692778</v>
+        <v>8.189139045230684</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2299910619096863</v>
+        <v>0.4566198734553241</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -662,16 +662,16 @@
         <v>203</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0864857590444</v>
+        <v>5.976800931683473</v>
       </c>
       <c r="E5" t="n">
-        <v>2.767526559323921</v>
+        <v>2.709151904491671</v>
       </c>
       <c r="F5" t="n">
-        <v>5.275448123668693</v>
+        <v>5.214419228200577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7105267273879203</v>
+        <v>0.7171855165485657</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>203</v>
       </c>
       <c r="D6" t="n">
-        <v>6.000803769673537</v>
+        <v>5.688832767254914</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6627651011469</v>
+        <v>2.523826393170964</v>
       </c>
       <c r="F6" t="n">
-        <v>5.333464416346492</v>
+        <v>5.1540648324339</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7041248021227725</v>
+        <v>0.7236945114040314</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -760,16 +760,16 @@
         <v>203</v>
       </c>
       <c r="D7" t="n">
-        <v>12.67904447374227</v>
+        <v>7.60637424087167</v>
       </c>
       <c r="E7" t="n">
-        <v>6.199859678247157</v>
+        <v>3.330552861664386</v>
       </c>
       <c r="F7" t="n">
-        <v>9.053472191828156</v>
+        <v>5.715011043595948</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1474495234600094</v>
+        <v>0.6602778175281689</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -809,16 +809,16 @@
         <v>234</v>
       </c>
       <c r="D8" t="n">
-        <v>5.503947012698498</v>
+        <v>5.506173843873867</v>
       </c>
       <c r="E8" t="n">
-        <v>4.618375436582778</v>
+        <v>4.620564072948108</v>
       </c>
       <c r="F8" t="n">
-        <v>11.22967598524945</v>
+        <v>11.23351494396772</v>
       </c>
       <c r="G8" t="n">
-        <v>0.516724948633329</v>
+        <v>0.5163944689125419</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>13.56293254451962</v>
+        <v>8.202621515052606</v>
       </c>
       <c r="E9" t="n">
-        <v>14.06390543319609</v>
+        <v>7.774651223153412</v>
       </c>
       <c r="F9" t="n">
-        <v>19.57208479661322</v>
+        <v>13.03510584383248</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4680271984640838</v>
+        <v>0.348837999929106</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -907,16 +907,16 @@
         <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>11.11757252065611</v>
+        <v>5.365430256508413</v>
       </c>
       <c r="E10" t="n">
-        <v>11.08684116555558</v>
+        <v>4.435603963414637</v>
       </c>
       <c r="F10" t="n">
-        <v>15.96858331402931</v>
+        <v>11.56245184173678</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02277920160870939</v>
+        <v>0.4876581898627955</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -956,16 +956,16 @@
         <v>234</v>
       </c>
       <c r="D11" t="n">
-        <v>4.295800144595013</v>
+        <v>4.296521282119063</v>
       </c>
       <c r="E11" t="n">
-        <v>3.932858840961659</v>
+        <v>3.933690533682205</v>
       </c>
       <c r="F11" t="n">
-        <v>8.889578621557694</v>
+        <v>8.891740785084931</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2965521284193977</v>
+        <v>0.2962098952575073</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1005,16 +1005,16 @@
         <v>234</v>
       </c>
       <c r="D12" t="n">
-        <v>9.433533752805115</v>
+        <v>5.489029906131228</v>
       </c>
       <c r="E12" t="n">
-        <v>9.508270380055633</v>
+        <v>5.151387124892636</v>
       </c>
       <c r="F12" t="n">
-        <v>12.9244615490271</v>
+        <v>8.801981751071031</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4869435693024888</v>
+        <v>0.3103472108172199</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1054,16 +1054,16 @@
         <v>234</v>
       </c>
       <c r="D13" t="n">
-        <v>8.012625712616954</v>
+        <v>4.480046400647806</v>
       </c>
       <c r="E13" t="n">
-        <v>7.965410476549016</v>
+        <v>4.124183619341564</v>
       </c>
       <c r="F13" t="n">
-        <v>11.44105689872277</v>
+        <v>9.414949375154155</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1652037139806954</v>
+        <v>0.2109481405708491</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         <v>234</v>
       </c>
       <c r="D14" t="n">
-        <v>2.257292839824642</v>
+        <v>2.257958702419534</v>
       </c>
       <c r="E14" t="n">
-        <v>2.411839192371335</v>
+        <v>2.412928237062234</v>
       </c>
       <c r="F14" t="n">
-        <v>7.954289216601523</v>
+        <v>7.953867317844638</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6351548356956079</v>
+        <v>0.6351935377429914</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>234</v>
       </c>
       <c r="D15" t="n">
-        <v>7.240780251485892</v>
+        <v>5.520566482949032</v>
       </c>
       <c r="E15" t="n">
-        <v>9.178163714670596</v>
+        <v>6.828135371531725</v>
       </c>
       <c r="F15" t="n">
-        <v>11.19566518503113</v>
+        <v>9.591203470101432</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2772208050725247</v>
+        <v>0.4695407249149222</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1201,16 +1201,16 @@
         <v>234</v>
       </c>
       <c r="D16" t="n">
-        <v>6.021769925483243</v>
+        <v>5.03762304146431</v>
       </c>
       <c r="E16" t="n">
-        <v>7.438204439875792</v>
+        <v>6.128557131679304</v>
       </c>
       <c r="F16" t="n">
-        <v>10.783571771579</v>
+        <v>9.305653959952801</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3294500951967373</v>
+        <v>0.5006562292614767</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1250,16 +1250,16 @@
         <v>234</v>
       </c>
       <c r="D17" t="n">
-        <v>3.541045909138147</v>
+        <v>3.541050075328585</v>
       </c>
       <c r="E17" t="n">
-        <v>2.984570972411286</v>
+        <v>2.984833126787453</v>
       </c>
       <c r="F17" t="n">
-        <v>9.636795959124711</v>
+        <v>9.637258101665145</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6073764754997955</v>
+        <v>0.6073388172605674</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1299,16 +1299,16 @@
         <v>234</v>
       </c>
       <c r="D18" t="n">
-        <v>6.404062237925282</v>
+        <v>4.467906739806385</v>
       </c>
       <c r="E18" t="n">
-        <v>6.206076404744769</v>
+        <v>4.032650755903138</v>
       </c>
       <c r="F18" t="n">
-        <v>8.927914667286146</v>
+        <v>7.838824557029978</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6630146265218528</v>
+        <v>0.7402157132836075</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         <v>234</v>
       </c>
       <c r="D19" t="n">
-        <v>5.759259863862858</v>
+        <v>5.279077456455199</v>
       </c>
       <c r="E19" t="n">
-        <v>5.377330824484067</v>
+        <v>4.946686562515644</v>
       </c>
       <c r="F19" t="n">
-        <v>11.9102742084685</v>
+        <v>11.18833490135035</v>
       </c>
       <c r="G19" t="n">
-        <v>0.400271744693631</v>
+        <v>0.4707731067842614</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1397,16 +1397,16 @@
         <v>213</v>
       </c>
       <c r="D20" t="n">
-        <v>6.914546868482034</v>
+        <v>7.014536543223783</v>
       </c>
       <c r="E20" t="n">
-        <v>2.628291897104535</v>
+        <v>2.561916513469902</v>
       </c>
       <c r="F20" t="n">
-        <v>3.775856572479338</v>
+        <v>4.017269162231092</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7252522406759934</v>
+        <v>0.6889966671759968</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1446,16 +1446,16 @@
         <v>213</v>
       </c>
       <c r="D21" t="n">
-        <v>7.681789547555446</v>
+        <v>6.892833286714121</v>
       </c>
       <c r="E21" t="n">
-        <v>2.703064009264373</v>
+        <v>2.605220520308225</v>
       </c>
       <c r="F21" t="n">
-        <v>3.814856253627946</v>
+        <v>3.826593723783812</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7195473569291837</v>
+        <v>0.7178189203188657</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1495,16 +1495,16 @@
         <v>213</v>
       </c>
       <c r="D22" t="n">
-        <v>7.531215584620392</v>
+        <v>7.507447691170269</v>
       </c>
       <c r="E22" t="n">
-        <v>2.668592610358417</v>
+        <v>2.844720631610776</v>
       </c>
       <c r="F22" t="n">
-        <v>3.876753823489376</v>
+        <v>4.102722877136087</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7103726111456587</v>
+        <v>0.6756248714952823</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1544,16 +1544,16 @@
         <v>213</v>
       </c>
       <c r="D23" t="n">
-        <v>8.310013182469508</v>
+        <v>8.094051632720722</v>
       </c>
       <c r="E23" t="n">
-        <v>2.768804497769296</v>
+        <v>2.678697060120434</v>
       </c>
       <c r="F23" t="n">
-        <v>4.660559898748315</v>
+        <v>4.282633933272701</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5279108308705944</v>
+        <v>0.6013702049559182</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>213</v>
       </c>
       <c r="D24" t="n">
-        <v>10.59869591759488</v>
+        <v>7.764594977199551</v>
       </c>
       <c r="E24" t="n">
-        <v>3.363195309150354</v>
+        <v>2.454616096368682</v>
       </c>
       <c r="F24" t="n">
-        <v>5.037048038015321</v>
+        <v>4.132495355500004</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4485577542149736</v>
+        <v>0.6288302306412163</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1642,16 +1642,16 @@
         <v>213</v>
       </c>
       <c r="D25" t="n">
-        <v>9.792670650301922</v>
+        <v>7.958710498753789</v>
       </c>
       <c r="E25" t="n">
-        <v>3.047561809257031</v>
+        <v>2.576755437423979</v>
       </c>
       <c r="F25" t="n">
-        <v>4.714574207131379</v>
+        <v>4.169641489174324</v>
       </c>
       <c r="G25" t="n">
-        <v>0.516904713062379</v>
+        <v>0.6221275063801326</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1691,16 +1691,16 @@
         <v>276</v>
       </c>
       <c r="D26" t="n">
-        <v>6.942901795769707</v>
+        <v>6.941966326255017</v>
       </c>
       <c r="E26" t="n">
-        <v>5.472142688975849</v>
+        <v>5.470575399659038</v>
       </c>
       <c r="F26" t="n">
-        <v>16.54079834570621</v>
+        <v>16.53993398154544</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9188709960649202</v>
+        <v>0.9188794748782994</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1740,16 +1740,16 @@
         <v>276</v>
       </c>
       <c r="D27" t="n">
-        <v>14.76437356829242</v>
+        <v>8.226158995796979</v>
       </c>
       <c r="E27" t="n">
-        <v>16.38180457423511</v>
+        <v>7.689717487901834</v>
       </c>
       <c r="F27" t="n">
-        <v>28.78120354009989</v>
+        <v>20.04579984119748</v>
       </c>
       <c r="G27" t="n">
-        <v>0.754370167839102</v>
+        <v>0.8808456260975959</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1789,16 +1789,16 @@
         <v>276</v>
       </c>
       <c r="D28" t="n">
-        <v>11.32169312369476</v>
+        <v>8.226158995796979</v>
       </c>
       <c r="E28" t="n">
-        <v>12.22954181132504</v>
+        <v>7.689717487901834</v>
       </c>
       <c r="F28" t="n">
-        <v>22.41959472589807</v>
+        <v>20.04579984119748</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8509545491074079</v>
+        <v>0.8808456260975959</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1838,16 +1838,16 @@
         <v>276</v>
       </c>
       <c r="D29" t="n">
-        <v>7.29517979256501</v>
+        <v>7.293640144385048</v>
       </c>
       <c r="E29" t="n">
-        <v>11.15462139875414</v>
+        <v>11.15174730213526</v>
       </c>
       <c r="F29" t="n">
-        <v>18.97973631052641</v>
+        <v>18.97818242173732</v>
       </c>
       <c r="G29" t="n">
-        <v>0.07575634502367157</v>
+        <v>0.07590767621605388</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1887,16 +1887,16 @@
         <v>276</v>
       </c>
       <c r="D30" t="n">
-        <v>21.85123707655707</v>
+        <v>8.533307851557119</v>
       </c>
       <c r="E30" t="n">
-        <v>33.6250420990585</v>
+        <v>13.09619714172012</v>
       </c>
       <c r="F30" t="n">
-        <v>40.54989051433547</v>
+        <v>19.20485355997385</v>
       </c>
       <c r="G30" t="n">
-        <v>-3.218766617977598</v>
+        <v>0.05370154962942786</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1936,16 +1936,16 @@
         <v>276</v>
       </c>
       <c r="D31" t="n">
-        <v>12.84559291283292</v>
+        <v>8.533307851557119</v>
       </c>
       <c r="E31" t="n">
-        <v>19.75635822675999</v>
+        <v>13.09619714172012</v>
       </c>
       <c r="F31" t="n">
-        <v>26.61372465755518</v>
+        <v>19.20485355997385</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.8172615919632893</v>
+        <v>0.05370154962942786</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1985,16 +1985,16 @@
         <v>213</v>
       </c>
       <c r="D32" t="n">
-        <v>7.409128287893188</v>
+        <v>7.100053092815831</v>
       </c>
       <c r="E32" t="n">
-        <v>2.593457805828454</v>
+        <v>2.470343544306012</v>
       </c>
       <c r="F32" t="n">
-        <v>3.495672442815243</v>
+        <v>3.390199402978767</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7747912657532339</v>
+        <v>0.7881764442358834</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2034,16 +2034,16 @@
         <v>213</v>
       </c>
       <c r="D33" t="n">
-        <v>6.65501983293405</v>
+        <v>6.778516069692492</v>
       </c>
       <c r="E33" t="n">
-        <v>2.263569947475957</v>
+        <v>2.326595256288697</v>
       </c>
       <c r="F33" t="n">
-        <v>3.267329231872592</v>
+        <v>3.291372438935524</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8032523451372638</v>
+        <v>0.8003460879679845</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2083,16 +2083,16 @@
         <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>8.038243618227868</v>
+        <v>7.862272269009213</v>
       </c>
       <c r="E34" t="n">
-        <v>2.630714025191922</v>
+        <v>2.718965435018927</v>
       </c>
       <c r="F34" t="n">
-        <v>3.667494929248991</v>
+        <v>3.843905664536912</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7521078284119701</v>
+        <v>0.7276864764818894</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2132,16 +2132,16 @@
         <v>213</v>
       </c>
       <c r="D35" t="n">
-        <v>7.623169754489648</v>
+        <v>7.595132782483467</v>
       </c>
       <c r="E35" t="n">
-        <v>2.459417664679759</v>
+        <v>2.471745370880807</v>
       </c>
       <c r="F35" t="n">
-        <v>3.585699267928486</v>
+        <v>3.524063157951415</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4739810586016601</v>
+        <v>0.4919095591238258</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
         <v>213</v>
       </c>
       <c r="D36" t="n">
-        <v>8.409529152993814</v>
+        <v>8.219049146370278</v>
       </c>
       <c r="E36" t="n">
-        <v>2.686670245758572</v>
+        <v>2.631271940256516</v>
       </c>
       <c r="F36" t="n">
-        <v>3.81798511102792</v>
+        <v>3.729986661255328</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4036213071998926</v>
+        <v>0.4307956435540213</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2230,16 +2230,16 @@
         <v>213</v>
       </c>
       <c r="D37" t="n">
-        <v>13.84199780817706</v>
+        <v>9.128732233559528</v>
       </c>
       <c r="E37" t="n">
-        <v>4.323162675903657</v>
+        <v>2.983925582466707</v>
       </c>
       <c r="F37" t="n">
-        <v>5.73075663185077</v>
+        <v>4.214182481438167</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.3436234941615954</v>
+        <v>0.2734251973294374</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>

--- a/Thesis Forecasting/metadata/overall_comparison/model_average_validation_testing_comparison.xlsx
+++ b/Thesis Forecasting/metadata/overall_comparison/model_average_validation_testing_comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$M$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$H$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -425,12 +425,7 @@
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="29" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,31 +466,6 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>evaluation_type</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>mape_rows_included</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>mape_rows_excluded</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>mape_rows_excluded_fraction</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>low_load_regime</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
           <t>split</t>
         </is>
       </c>
@@ -528,23 +498,6 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.01219512195121951</v>
-      </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -577,23 +530,6 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J3" t="n">
-        <v>24</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.01219512195121951</v>
-      </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -626,23 +562,6 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.01219512195121951</v>
-      </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -675,23 +594,6 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -724,23 +626,6 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -773,23 +658,6 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -822,23 +690,6 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -871,23 +722,6 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -920,23 +754,6 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -969,23 +786,6 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1018,23 +818,6 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1067,23 +850,6 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1116,23 +882,6 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -1165,23 +914,6 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -1214,23 +946,6 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -1263,23 +978,6 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="b">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1312,23 +1010,6 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1361,23 +1042,6 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="b">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1410,23 +1074,6 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -1459,23 +1106,6 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="b">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -1508,23 +1138,6 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -1557,23 +1170,6 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1606,23 +1202,6 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="b">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1655,23 +1234,6 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="b">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1704,23 +1266,6 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="b">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -1753,23 +1298,6 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="b">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -1802,23 +1330,6 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="b">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -1851,23 +1362,6 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1900,23 +1394,6 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="b">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1949,23 +1426,6 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="b">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -1998,23 +1458,6 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="b">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -2047,23 +1490,6 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="b">
-        <v>0</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -2096,23 +1522,6 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
           <t>testing</t>
         </is>
       </c>
@@ -2145,23 +1554,6 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="b">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -2194,23 +1586,6 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="b">
-        <v>0</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
@@ -2243,29 +1618,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="b">
-        <v>0</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
           <t>validation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M37"/>
+  <autoFilter ref="A1:H37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Thesis Forecasting/metadata/overall_comparison/model_average_validation_testing_comparison.xlsx
+++ b/Thesis Forecasting/metadata/overall_comparison/model_average_validation_testing_comparison.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,42 +441,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>plant</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>feature_count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MAPE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>split</t>
         </is>
